--- a/db/data/project_item_categories.xlsx
+++ b/db/data/project_item_categories.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pradeep\Desktop\storemgmt\db\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53B6639-15FC-4442-B328-914CD2074818}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F60D180-D86D-4F85-8C79-F839B890660B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10935" yWindow="465" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" r:id="rId1"/>
@@ -893,7 +893,7 @@
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.875" customWidth="1"/>
     <col min="4" max="4" width="23.125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="8.75" bestFit="1" customWidth="1"/>
   </cols>
